--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1419,6 +1419,24 @@
   </si>
   <si>
     <t xml:space="preserve">2026-01-17 13:28:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22 11:36:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22 13:36:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.105447,6.943168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.150477,6.893747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 mins</t>
   </si>
 </sst>
 </file>
@@ -10439,6 +10457,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" t="s">
+        <v>470</v>
+      </c>
+      <c r="C213" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" t="s">
+        <v>471</v>
+      </c>
+      <c r="E213" t="s">
+        <v>472</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G213" t="s">
+        <v>473</v>
+      </c>
+      <c r="H213" t="n">
+        <v>634</v>
+      </c>
+      <c r="I213" t="s">
+        <v>474</v>
+      </c>
+      <c r="J213" t="n">
+        <v>651</v>
+      </c>
+      <c r="K213" t="s">
+        <v>474</v>
+      </c>
+      <c r="L213" t="s">
+        <v>90</v>
+      </c>
+      <c r="M213" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1437,6 +1437,15 @@
   </si>
   <si>
     <t xml:space="preserve">11 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22 18:59:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22 20:59:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 mins</t>
   </si>
 </sst>
 </file>
@@ -10498,6 +10507,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>475</v>
+      </c>
+      <c r="B214" t="s">
+        <v>476</v>
+      </c>
+      <c r="C214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214" t="s">
+        <v>471</v>
+      </c>
+      <c r="E214" t="s">
+        <v>472</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G214" t="s">
+        <v>473</v>
+      </c>
+      <c r="H214" t="n">
+        <v>634</v>
+      </c>
+      <c r="I214" t="s">
+        <v>474</v>
+      </c>
+      <c r="J214" t="n">
+        <v>591</v>
+      </c>
+      <c r="K214" t="s">
+        <v>477</v>
+      </c>
+      <c r="L214" t="s">
+        <v>90</v>
+      </c>
+      <c r="M214" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1446,6 +1446,12 @@
   </si>
   <si>
     <t xml:space="preserve">10 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 06:03:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 08:03:24</t>
   </si>
 </sst>
 </file>
@@ -10548,6 +10554,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" t="s">
+        <v>15</v>
+      </c>
+      <c r="D215" t="s">
+        <v>471</v>
+      </c>
+      <c r="E215" t="s">
+        <v>472</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G215" t="s">
+        <v>473</v>
+      </c>
+      <c r="H215" t="n">
+        <v>634</v>
+      </c>
+      <c r="I215" t="s">
+        <v>474</v>
+      </c>
+      <c r="J215" t="n">
+        <v>632</v>
+      </c>
+      <c r="K215" t="s">
+        <v>474</v>
+      </c>
+      <c r="L215" t="s">
+        <v>124</v>
+      </c>
+      <c r="M215" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1452,6 +1452,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-23 08:03:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 11:38:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 13:38:10</t>
   </si>
 </sst>
 </file>
@@ -10595,6 +10601,47 @@
         <v>8</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" t="s">
+        <v>481</v>
+      </c>
+      <c r="C216" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216" t="s">
+        <v>471</v>
+      </c>
+      <c r="E216" t="s">
+        <v>472</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G216" t="s">
+        <v>473</v>
+      </c>
+      <c r="H216" t="n">
+        <v>634</v>
+      </c>
+      <c r="I216" t="s">
+        <v>474</v>
+      </c>
+      <c r="J216" t="n">
+        <v>639</v>
+      </c>
+      <c r="K216" t="s">
+        <v>474</v>
+      </c>
+      <c r="L216" t="s">
+        <v>124</v>
+      </c>
+      <c r="M216" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1458,6 +1458,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-23 13:38:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 16:58:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 18:58:44</t>
   </si>
 </sst>
 </file>
@@ -10642,6 +10648,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>482</v>
+      </c>
+      <c r="B217" t="s">
+        <v>483</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" t="s">
+        <v>471</v>
+      </c>
+      <c r="E217" t="s">
+        <v>472</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G217" t="s">
+        <v>473</v>
+      </c>
+      <c r="H217" t="n">
+        <v>606</v>
+      </c>
+      <c r="I217" t="s">
+        <v>477</v>
+      </c>
+      <c r="J217" t="n">
+        <v>611</v>
+      </c>
+      <c r="K217" t="s">
+        <v>477</v>
+      </c>
+      <c r="L217" t="s">
+        <v>124</v>
+      </c>
+      <c r="M217" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="486">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1464,6 +1464,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-23 18:58:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 20:26:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 22:26:16</t>
   </si>
 </sst>
 </file>
@@ -10689,6 +10695,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>484</v>
+      </c>
+      <c r="B218" t="s">
+        <v>485</v>
+      </c>
+      <c r="C218" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218" t="s">
+        <v>471</v>
+      </c>
+      <c r="E218" t="s">
+        <v>472</v>
+      </c>
+      <c r="F218" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G218" t="s">
+        <v>473</v>
+      </c>
+      <c r="H218" t="n">
+        <v>634</v>
+      </c>
+      <c r="I218" t="s">
+        <v>474</v>
+      </c>
+      <c r="J218" t="n">
+        <v>578</v>
+      </c>
+      <c r="K218" t="s">
+        <v>477</v>
+      </c>
+      <c r="L218" t="s">
+        <v>124</v>
+      </c>
+      <c r="M218" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1470,6 +1470,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-23 22:26:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24 14:18:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24 16:18:50</t>
   </si>
 </sst>
 </file>
@@ -10736,6 +10742,47 @@
         <v>22</v>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>486</v>
+      </c>
+      <c r="B219" t="s">
+        <v>487</v>
+      </c>
+      <c r="C219" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219" t="s">
+        <v>471</v>
+      </c>
+      <c r="E219" t="s">
+        <v>472</v>
+      </c>
+      <c r="F219" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G219" t="s">
+        <v>473</v>
+      </c>
+      <c r="H219" t="n">
+        <v>633</v>
+      </c>
+      <c r="I219" t="s">
+        <v>474</v>
+      </c>
+      <c r="J219" t="n">
+        <v>678</v>
+      </c>
+      <c r="K219" t="s">
+        <v>474</v>
+      </c>
+      <c r="L219" t="s">
+        <v>162</v>
+      </c>
+      <c r="M219" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1476,6 +1476,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-24 16:18:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24 18:32:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24 20:32:21</t>
   </si>
 </sst>
 </file>
@@ -10783,6 +10789,47 @@
         <v>16</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>488</v>
+      </c>
+      <c r="B220" t="s">
+        <v>489</v>
+      </c>
+      <c r="C220" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220" t="s">
+        <v>471</v>
+      </c>
+      <c r="E220" t="s">
+        <v>472</v>
+      </c>
+      <c r="F220" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G220" t="s">
+        <v>473</v>
+      </c>
+      <c r="H220" t="n">
+        <v>633</v>
+      </c>
+      <c r="I220" t="s">
+        <v>474</v>
+      </c>
+      <c r="J220" t="n">
+        <v>602</v>
+      </c>
+      <c r="K220" t="s">
+        <v>477</v>
+      </c>
+      <c r="L220" t="s">
+        <v>162</v>
+      </c>
+      <c r="M220" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1482,6 +1482,15 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-24 20:32:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 10:17:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 12:17:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 mins</t>
   </si>
 </sst>
 </file>
@@ -10830,6 +10839,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>490</v>
+      </c>
+      <c r="B221" t="s">
+        <v>491</v>
+      </c>
+      <c r="C221" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221" t="s">
+        <v>471</v>
+      </c>
+      <c r="E221" t="s">
+        <v>472</v>
+      </c>
+      <c r="F221" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G221" t="s">
+        <v>473</v>
+      </c>
+      <c r="H221" t="n">
+        <v>689</v>
+      </c>
+      <c r="I221" t="s">
+        <v>474</v>
+      </c>
+      <c r="J221" t="n">
+        <v>696</v>
+      </c>
+      <c r="K221" t="s">
+        <v>492</v>
+      </c>
+      <c r="L221" t="s">
+        <v>196</v>
+      </c>
+      <c r="M221" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1491,6 +1491,12 @@
   </si>
   <si>
     <t xml:space="preserve">12 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 15:20:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 17:20:08</t>
   </si>
 </sst>
 </file>
@@ -10880,6 +10886,47 @@
         <v>12</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>493</v>
+      </c>
+      <c r="B222" t="s">
+        <v>494</v>
+      </c>
+      <c r="C222" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" t="s">
+        <v>471</v>
+      </c>
+      <c r="E222" t="s">
+        <v>472</v>
+      </c>
+      <c r="F222" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G222" t="s">
+        <v>473</v>
+      </c>
+      <c r="H222" t="n">
+        <v>633</v>
+      </c>
+      <c r="I222" t="s">
+        <v>474</v>
+      </c>
+      <c r="J222" t="n">
+        <v>627</v>
+      </c>
+      <c r="K222" t="s">
+        <v>477</v>
+      </c>
+      <c r="L222" t="s">
+        <v>196</v>
+      </c>
+      <c r="M222" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1497,6 +1497,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-25 17:20:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 19:21:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 21:21:28</t>
   </si>
 </sst>
 </file>
@@ -10927,6 +10933,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>495</v>
+      </c>
+      <c r="B223" t="s">
+        <v>496</v>
+      </c>
+      <c r="C223" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223" t="s">
+        <v>471</v>
+      </c>
+      <c r="E223" t="s">
+        <v>472</v>
+      </c>
+      <c r="F223" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G223" t="s">
+        <v>473</v>
+      </c>
+      <c r="H223" t="n">
+        <v>593</v>
+      </c>
+      <c r="I223" t="s">
+        <v>477</v>
+      </c>
+      <c r="J223" t="n">
+        <v>598</v>
+      </c>
+      <c r="K223" t="s">
+        <v>477</v>
+      </c>
+      <c r="L223" t="s">
+        <v>196</v>
+      </c>
+      <c r="M223" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1503,6 +1503,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-25 21:21:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 09:58:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 11:58:49</t>
   </si>
 </sst>
 </file>
@@ -10974,6 +10980,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>497</v>
+      </c>
+      <c r="B224" t="s">
+        <v>498</v>
+      </c>
+      <c r="C224" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" t="s">
+        <v>471</v>
+      </c>
+      <c r="E224" t="s">
+        <v>472</v>
+      </c>
+      <c r="F224" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G224" t="s">
+        <v>473</v>
+      </c>
+      <c r="H224" t="n">
+        <v>633</v>
+      </c>
+      <c r="I224" t="s">
+        <v>474</v>
+      </c>
+      <c r="J224" t="n">
+        <v>641</v>
+      </c>
+      <c r="K224" t="s">
+        <v>474</v>
+      </c>
+      <c r="L224" t="s">
+        <v>230</v>
+      </c>
+      <c r="M224" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1509,6 +1509,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-26 11:58:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 14:33:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 16:33:46</t>
   </si>
 </sst>
 </file>
@@ -11021,6 +11027,47 @@
         <v>11</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>499</v>
+      </c>
+      <c r="B225" t="s">
+        <v>500</v>
+      </c>
+      <c r="C225" t="s">
+        <v>15</v>
+      </c>
+      <c r="D225" t="s">
+        <v>471</v>
+      </c>
+      <c r="E225" t="s">
+        <v>472</v>
+      </c>
+      <c r="F225" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G225" t="s">
+        <v>473</v>
+      </c>
+      <c r="H225" t="n">
+        <v>633</v>
+      </c>
+      <c r="I225" t="s">
+        <v>474</v>
+      </c>
+      <c r="J225" t="n">
+        <v>612</v>
+      </c>
+      <c r="K225" t="s">
+        <v>477</v>
+      </c>
+      <c r="L225" t="s">
+        <v>230</v>
+      </c>
+      <c r="M225" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1515,6 +1515,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-26 16:33:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 18:42:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-26 20:42:44</t>
   </si>
 </sst>
 </file>
@@ -11068,6 +11074,47 @@
         <v>16</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>501</v>
+      </c>
+      <c r="B226" t="s">
+        <v>502</v>
+      </c>
+      <c r="C226" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" t="s">
+        <v>471</v>
+      </c>
+      <c r="E226" t="s">
+        <v>472</v>
+      </c>
+      <c r="F226" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G226" t="s">
+        <v>473</v>
+      </c>
+      <c r="H226" t="n">
+        <v>633</v>
+      </c>
+      <c r="I226" t="s">
+        <v>474</v>
+      </c>
+      <c r="J226" t="n">
+        <v>619</v>
+      </c>
+      <c r="K226" t="s">
+        <v>477</v>
+      </c>
+      <c r="L226" t="s">
+        <v>230</v>
+      </c>
+      <c r="M226" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1521,6 +1521,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-26 20:42:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 10:39:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 12:39:41</t>
   </si>
 </sst>
 </file>
@@ -11115,6 +11121,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>503</v>
+      </c>
+      <c r="B227" t="s">
+        <v>504</v>
+      </c>
+      <c r="C227" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227" t="s">
+        <v>471</v>
+      </c>
+      <c r="E227" t="s">
+        <v>472</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G227" t="s">
+        <v>473</v>
+      </c>
+      <c r="H227" t="n">
+        <v>633</v>
+      </c>
+      <c r="I227" t="s">
+        <v>474</v>
+      </c>
+      <c r="J227" t="n">
+        <v>604</v>
+      </c>
+      <c r="K227" t="s">
+        <v>477</v>
+      </c>
+      <c r="L227" t="s">
+        <v>21</v>
+      </c>
+      <c r="M227" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1527,6 +1527,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-27 12:39:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 15:46:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 17:46:28</t>
   </si>
 </sst>
 </file>
@@ -11162,6 +11168,47 @@
         <v>12</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>505</v>
+      </c>
+      <c r="B228" t="s">
+        <v>506</v>
+      </c>
+      <c r="C228" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" t="s">
+        <v>471</v>
+      </c>
+      <c r="E228" t="s">
+        <v>472</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G228" t="s">
+        <v>473</v>
+      </c>
+      <c r="H228" t="n">
+        <v>633</v>
+      </c>
+      <c r="I228" t="s">
+        <v>474</v>
+      </c>
+      <c r="J228" t="n">
+        <v>604</v>
+      </c>
+      <c r="K228" t="s">
+        <v>477</v>
+      </c>
+      <c r="L228" t="s">
+        <v>21</v>
+      </c>
+      <c r="M228" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1533,6 +1533,15 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-27 17:46:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 19:50:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27 21:50:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 mins</t>
   </si>
 </sst>
 </file>
@@ -11209,6 +11218,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>507</v>
+      </c>
+      <c r="B229" t="s">
+        <v>508</v>
+      </c>
+      <c r="C229" t="s">
+        <v>15</v>
+      </c>
+      <c r="D229" t="s">
+        <v>471</v>
+      </c>
+      <c r="E229" t="s">
+        <v>472</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G229" t="s">
+        <v>473</v>
+      </c>
+      <c r="H229" t="n">
+        <v>633</v>
+      </c>
+      <c r="I229" t="s">
+        <v>474</v>
+      </c>
+      <c r="J229" t="n">
+        <v>562</v>
+      </c>
+      <c r="K229" t="s">
+        <v>509</v>
+      </c>
+      <c r="L229" t="s">
+        <v>21</v>
+      </c>
+      <c r="M229" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1542,6 +1542,12 @@
   </si>
   <si>
     <t xml:space="preserve">9 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28 11:47:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28 13:47:12</t>
   </si>
 </sst>
 </file>
@@ -11259,6 +11265,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>510</v>
+      </c>
+      <c r="B230" t="s">
+        <v>511</v>
+      </c>
+      <c r="C230" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" t="s">
+        <v>471</v>
+      </c>
+      <c r="E230" t="s">
+        <v>472</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G230" t="s">
+        <v>473</v>
+      </c>
+      <c r="H230" t="n">
+        <v>633</v>
+      </c>
+      <c r="I230" t="s">
+        <v>474</v>
+      </c>
+      <c r="J230" t="n">
+        <v>631</v>
+      </c>
+      <c r="K230" t="s">
+        <v>474</v>
+      </c>
+      <c r="L230" t="s">
+        <v>48</v>
+      </c>
+      <c r="M230" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1548,6 +1548,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-28 13:47:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28 19:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28 21:47:30</t>
   </si>
 </sst>
 </file>
@@ -11306,6 +11312,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>512</v>
+      </c>
+      <c r="B231" t="s">
+        <v>513</v>
+      </c>
+      <c r="C231" t="s">
+        <v>15</v>
+      </c>
+      <c r="D231" t="s">
+        <v>471</v>
+      </c>
+      <c r="E231" t="s">
+        <v>472</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G231" t="s">
+        <v>473</v>
+      </c>
+      <c r="H231" t="n">
+        <v>633</v>
+      </c>
+      <c r="I231" t="s">
+        <v>474</v>
+      </c>
+      <c r="J231" t="n">
+        <v>582</v>
+      </c>
+      <c r="K231" t="s">
+        <v>477</v>
+      </c>
+      <c r="L231" t="s">
+        <v>48</v>
+      </c>
+      <c r="M231" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1554,6 +1554,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-28 21:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 11:27:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 13:27:07</t>
   </si>
 </sst>
 </file>
@@ -11353,6 +11359,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>514</v>
+      </c>
+      <c r="B232" t="s">
+        <v>515</v>
+      </c>
+      <c r="C232" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" t="s">
+        <v>471</v>
+      </c>
+      <c r="E232" t="s">
+        <v>472</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G232" t="s">
+        <v>473</v>
+      </c>
+      <c r="H232" t="n">
+        <v>633</v>
+      </c>
+      <c r="I232" t="s">
+        <v>474</v>
+      </c>
+      <c r="J232" t="n">
+        <v>659</v>
+      </c>
+      <c r="K232" t="s">
+        <v>474</v>
+      </c>
+      <c r="L232" t="s">
+        <v>90</v>
+      </c>
+      <c r="M232" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1560,6 +1560,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-29 13:27:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 18:10:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 20:10:47</t>
   </si>
 </sst>
 </file>
@@ -11400,6 +11406,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>516</v>
+      </c>
+      <c r="B233" t="s">
+        <v>517</v>
+      </c>
+      <c r="C233" t="s">
+        <v>15</v>
+      </c>
+      <c r="D233" t="s">
+        <v>471</v>
+      </c>
+      <c r="E233" t="s">
+        <v>472</v>
+      </c>
+      <c r="F233" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G233" t="s">
+        <v>473</v>
+      </c>
+      <c r="H233" t="n">
+        <v>633</v>
+      </c>
+      <c r="I233" t="s">
+        <v>474</v>
+      </c>
+      <c r="J233" t="n">
+        <v>629</v>
+      </c>
+      <c r="K233" t="s">
+        <v>477</v>
+      </c>
+      <c r="L233" t="s">
+        <v>90</v>
+      </c>
+      <c r="M233" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1566,6 +1566,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-29 20:10:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30 11:16:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30 13:16:32</t>
   </si>
 </sst>
 </file>
@@ -11447,6 +11453,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>518</v>
+      </c>
+      <c r="B234" t="s">
+        <v>519</v>
+      </c>
+      <c r="C234" t="s">
+        <v>15</v>
+      </c>
+      <c r="D234" t="s">
+        <v>471</v>
+      </c>
+      <c r="E234" t="s">
+        <v>472</v>
+      </c>
+      <c r="F234" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G234" t="s">
+        <v>473</v>
+      </c>
+      <c r="H234" t="n">
+        <v>633</v>
+      </c>
+      <c r="I234" t="s">
+        <v>474</v>
+      </c>
+      <c r="J234" t="n">
+        <v>650</v>
+      </c>
+      <c r="K234" t="s">
+        <v>474</v>
+      </c>
+      <c r="L234" t="s">
+        <v>124</v>
+      </c>
+      <c r="M234" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1572,6 +1572,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-30 13:16:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30 16:55:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30 18:55:12</t>
   </si>
 </sst>
 </file>
@@ -11494,6 +11500,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>520</v>
+      </c>
+      <c r="B235" t="s">
+        <v>521</v>
+      </c>
+      <c r="C235" t="s">
+        <v>15</v>
+      </c>
+      <c r="D235" t="s">
+        <v>471</v>
+      </c>
+      <c r="E235" t="s">
+        <v>472</v>
+      </c>
+      <c r="F235" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G235" t="s">
+        <v>473</v>
+      </c>
+      <c r="H235" t="n">
+        <v>633</v>
+      </c>
+      <c r="I235" t="s">
+        <v>474</v>
+      </c>
+      <c r="J235" t="n">
+        <v>603</v>
+      </c>
+      <c r="K235" t="s">
+        <v>477</v>
+      </c>
+      <c r="L235" t="s">
+        <v>124</v>
+      </c>
+      <c r="M235" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1578,6 +1578,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-30 18:55:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 11:43:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 13:43:04</t>
   </si>
 </sst>
 </file>
@@ -11541,6 +11547,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>522</v>
+      </c>
+      <c r="B236" t="s">
+        <v>523</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236" t="s">
+        <v>471</v>
+      </c>
+      <c r="E236" t="s">
+        <v>472</v>
+      </c>
+      <c r="F236" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G236" t="s">
+        <v>473</v>
+      </c>
+      <c r="H236" t="n">
+        <v>633</v>
+      </c>
+      <c r="I236" t="s">
+        <v>474</v>
+      </c>
+      <c r="J236" t="n">
+        <v>675</v>
+      </c>
+      <c r="K236" t="s">
+        <v>474</v>
+      </c>
+      <c r="L236" t="s">
+        <v>162</v>
+      </c>
+      <c r="M236" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1584,6 +1584,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-01 13:43:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 18:33:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 20:33:05</t>
   </si>
 </sst>
 </file>
@@ -11588,6 +11594,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>524</v>
+      </c>
+      <c r="B237" t="s">
+        <v>525</v>
+      </c>
+      <c r="C237" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" t="s">
+        <v>471</v>
+      </c>
+      <c r="E237" t="s">
+        <v>472</v>
+      </c>
+      <c r="F237" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G237" t="s">
+        <v>473</v>
+      </c>
+      <c r="H237" t="n">
+        <v>633</v>
+      </c>
+      <c r="I237" t="s">
+        <v>474</v>
+      </c>
+      <c r="J237" t="n">
+        <v>614</v>
+      </c>
+      <c r="K237" t="s">
+        <v>477</v>
+      </c>
+      <c r="L237" t="s">
+        <v>162</v>
+      </c>
+      <c r="M237" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1590,6 +1590,15 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-01 20:33:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02 11:12:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02 13:12:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3 km</t>
   </si>
 </sst>
 </file>
@@ -11635,6 +11644,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>526</v>
+      </c>
+      <c r="B238" t="s">
+        <v>527</v>
+      </c>
+      <c r="C238" t="s">
+        <v>15</v>
+      </c>
+      <c r="D238" t="s">
+        <v>471</v>
+      </c>
+      <c r="E238" t="s">
+        <v>472</v>
+      </c>
+      <c r="F238" t="n">
+        <v>8271</v>
+      </c>
+      <c r="G238" t="s">
+        <v>528</v>
+      </c>
+      <c r="H238" t="n">
+        <v>724</v>
+      </c>
+      <c r="I238" t="s">
+        <v>492</v>
+      </c>
+      <c r="J238" t="n">
+        <v>865</v>
+      </c>
+      <c r="K238" t="s">
+        <v>20</v>
+      </c>
+      <c r="L238" t="s">
+        <v>196</v>
+      </c>
+      <c r="M238" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1599,6 +1599,12 @@
   </si>
   <si>
     <t xml:space="preserve">8.3 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02 16:43:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02 18:43:28</t>
   </si>
 </sst>
 </file>
@@ -11685,6 +11691,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>529</v>
+      </c>
+      <c r="B239" t="s">
+        <v>530</v>
+      </c>
+      <c r="C239" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239" t="s">
+        <v>471</v>
+      </c>
+      <c r="E239" t="s">
+        <v>472</v>
+      </c>
+      <c r="F239" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G239" t="s">
+        <v>473</v>
+      </c>
+      <c r="H239" t="n">
+        <v>633</v>
+      </c>
+      <c r="I239" t="s">
+        <v>474</v>
+      </c>
+      <c r="J239" t="n">
+        <v>793</v>
+      </c>
+      <c r="K239" t="s">
+        <v>266</v>
+      </c>
+      <c r="L239" t="s">
+        <v>196</v>
+      </c>
+      <c r="M239" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="533">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1605,6 +1605,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-02 18:43:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 10:30:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 12:30:48</t>
   </si>
 </sst>
 </file>
@@ -11732,6 +11738,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>531</v>
+      </c>
+      <c r="B240" t="s">
+        <v>532</v>
+      </c>
+      <c r="C240" t="s">
+        <v>15</v>
+      </c>
+      <c r="D240" t="s">
+        <v>471</v>
+      </c>
+      <c r="E240" t="s">
+        <v>472</v>
+      </c>
+      <c r="F240" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G240" t="s">
+        <v>473</v>
+      </c>
+      <c r="H240" t="n">
+        <v>633</v>
+      </c>
+      <c r="I240" t="s">
+        <v>474</v>
+      </c>
+      <c r="J240" t="n">
+        <v>584</v>
+      </c>
+      <c r="K240" t="s">
+        <v>477</v>
+      </c>
+      <c r="L240" t="s">
+        <v>230</v>
+      </c>
+      <c r="M240" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1611,6 +1611,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-03 12:30:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 15:16:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 17:16:09</t>
   </si>
 </sst>
 </file>
@@ -11779,6 +11785,47 @@
         <v>12</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>533</v>
+      </c>
+      <c r="B241" t="s">
+        <v>534</v>
+      </c>
+      <c r="C241" t="s">
+        <v>15</v>
+      </c>
+      <c r="D241" t="s">
+        <v>471</v>
+      </c>
+      <c r="E241" t="s">
+        <v>472</v>
+      </c>
+      <c r="F241" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G241" t="s">
+        <v>473</v>
+      </c>
+      <c r="H241" t="n">
+        <v>633</v>
+      </c>
+      <c r="I241" t="s">
+        <v>474</v>
+      </c>
+      <c r="J241" t="n">
+        <v>565</v>
+      </c>
+      <c r="K241" t="s">
+        <v>509</v>
+      </c>
+      <c r="L241" t="s">
+        <v>230</v>
+      </c>
+      <c r="M241" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="537">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1617,6 +1617,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-03 17:16:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 18:46:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03 20:46:46</t>
   </si>
 </sst>
 </file>
@@ -11826,6 +11832,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>535</v>
+      </c>
+      <c r="B242" t="s">
+        <v>536</v>
+      </c>
+      <c r="C242" t="s">
+        <v>15</v>
+      </c>
+      <c r="D242" t="s">
+        <v>471</v>
+      </c>
+      <c r="E242" t="s">
+        <v>472</v>
+      </c>
+      <c r="F242" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G242" t="s">
+        <v>473</v>
+      </c>
+      <c r="H242" t="n">
+        <v>633</v>
+      </c>
+      <c r="I242" t="s">
+        <v>474</v>
+      </c>
+      <c r="J242" t="n">
+        <v>593</v>
+      </c>
+      <c r="K242" t="s">
+        <v>477</v>
+      </c>
+      <c r="L242" t="s">
+        <v>230</v>
+      </c>
+      <c r="M242" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1623,6 +1623,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-03 20:46:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 11:11:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 13:11:29</t>
   </si>
 </sst>
 </file>
@@ -11873,6 +11879,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>537</v>
+      </c>
+      <c r="B243" t="s">
+        <v>538</v>
+      </c>
+      <c r="C243" t="s">
+        <v>15</v>
+      </c>
+      <c r="D243" t="s">
+        <v>471</v>
+      </c>
+      <c r="E243" t="s">
+        <v>472</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G243" t="s">
+        <v>473</v>
+      </c>
+      <c r="H243" t="n">
+        <v>633</v>
+      </c>
+      <c r="I243" t="s">
+        <v>474</v>
+      </c>
+      <c r="J243" t="n">
+        <v>710</v>
+      </c>
+      <c r="K243" t="s">
+        <v>492</v>
+      </c>
+      <c r="L243" t="s">
+        <v>21</v>
+      </c>
+      <c r="M243" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1629,6 +1629,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-04 13:11:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 15:54:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 17:54:38</t>
   </si>
 </sst>
 </file>
@@ -11920,6 +11926,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>539</v>
+      </c>
+      <c r="B244" t="s">
+        <v>540</v>
+      </c>
+      <c r="C244" t="s">
+        <v>15</v>
+      </c>
+      <c r="D244" t="s">
+        <v>471</v>
+      </c>
+      <c r="E244" t="s">
+        <v>472</v>
+      </c>
+      <c r="F244" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G244" t="s">
+        <v>473</v>
+      </c>
+      <c r="H244" t="n">
+        <v>633</v>
+      </c>
+      <c r="I244" t="s">
+        <v>474</v>
+      </c>
+      <c r="J244" t="n">
+        <v>740</v>
+      </c>
+      <c r="K244" t="s">
+        <v>492</v>
+      </c>
+      <c r="L244" t="s">
+        <v>21</v>
+      </c>
+      <c r="M244" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="543">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1635,6 +1635,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-04 17:54:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 19:41:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04 21:41:27</t>
   </si>
 </sst>
 </file>
@@ -11967,6 +11973,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>541</v>
+      </c>
+      <c r="B245" t="s">
+        <v>542</v>
+      </c>
+      <c r="C245" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" t="s">
+        <v>471</v>
+      </c>
+      <c r="E245" t="s">
+        <v>472</v>
+      </c>
+      <c r="F245" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G245" t="s">
+        <v>473</v>
+      </c>
+      <c r="H245" t="n">
+        <v>633</v>
+      </c>
+      <c r="I245" t="s">
+        <v>474</v>
+      </c>
+      <c r="J245" t="n">
+        <v>544</v>
+      </c>
+      <c r="K245" t="s">
+        <v>509</v>
+      </c>
+      <c r="L245" t="s">
+        <v>21</v>
+      </c>
+      <c r="M245" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="545">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1641,6 +1641,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-04 21:41:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05 12:21:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05 14:21:57</t>
   </si>
 </sst>
 </file>
@@ -12014,6 +12020,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>543</v>
+      </c>
+      <c r="B246" t="s">
+        <v>544</v>
+      </c>
+      <c r="C246" t="s">
+        <v>15</v>
+      </c>
+      <c r="D246" t="s">
+        <v>471</v>
+      </c>
+      <c r="E246" t="s">
+        <v>472</v>
+      </c>
+      <c r="F246" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G246" t="s">
+        <v>473</v>
+      </c>
+      <c r="H246" t="n">
+        <v>633</v>
+      </c>
+      <c r="I246" t="s">
+        <v>474</v>
+      </c>
+      <c r="J246" t="n">
+        <v>910</v>
+      </c>
+      <c r="K246" t="s">
+        <v>26</v>
+      </c>
+      <c r="L246" t="s">
+        <v>48</v>
+      </c>
+      <c r="M246" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="547">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1647,6 +1647,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-05 14:21:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05 20:42:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05 22:42:15</t>
   </si>
 </sst>
 </file>
@@ -12061,6 +12067,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>545</v>
+      </c>
+      <c r="B247" t="s">
+        <v>546</v>
+      </c>
+      <c r="C247" t="s">
+        <v>15</v>
+      </c>
+      <c r="D247" t="s">
+        <v>471</v>
+      </c>
+      <c r="E247" t="s">
+        <v>472</v>
+      </c>
+      <c r="F247" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G247" t="s">
+        <v>473</v>
+      </c>
+      <c r="H247" t="n">
+        <v>633</v>
+      </c>
+      <c r="I247" t="s">
+        <v>474</v>
+      </c>
+      <c r="J247" t="n">
+        <v>554</v>
+      </c>
+      <c r="K247" t="s">
+        <v>509</v>
+      </c>
+      <c r="L247" t="s">
+        <v>48</v>
+      </c>
+      <c r="M247" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="549">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1653,6 +1653,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-05 22:42:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06 12:08:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06 14:08:22</t>
   </si>
 </sst>
 </file>
@@ -12108,6 +12114,47 @@
         <v>22</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>547</v>
+      </c>
+      <c r="B248" t="s">
+        <v>548</v>
+      </c>
+      <c r="C248" t="s">
+        <v>15</v>
+      </c>
+      <c r="D248" t="s">
+        <v>471</v>
+      </c>
+      <c r="E248" t="s">
+        <v>472</v>
+      </c>
+      <c r="F248" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G248" t="s">
+        <v>473</v>
+      </c>
+      <c r="H248" t="n">
+        <v>750</v>
+      </c>
+      <c r="I248" t="s">
+        <v>266</v>
+      </c>
+      <c r="J248" t="n">
+        <v>751</v>
+      </c>
+      <c r="K248" t="s">
+        <v>266</v>
+      </c>
+      <c r="L248" t="s">
+        <v>90</v>
+      </c>
+      <c r="M248" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="551">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1659,6 +1659,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-06 14:08:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06 18:26:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06 20:26:08</t>
   </si>
 </sst>
 </file>
@@ -12155,6 +12161,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>549</v>
+      </c>
+      <c r="B249" t="s">
+        <v>550</v>
+      </c>
+      <c r="C249" t="s">
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>471</v>
+      </c>
+      <c r="E249" t="s">
+        <v>472</v>
+      </c>
+      <c r="F249" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G249" t="s">
+        <v>473</v>
+      </c>
+      <c r="H249" t="n">
+        <v>633</v>
+      </c>
+      <c r="I249" t="s">
+        <v>474</v>
+      </c>
+      <c r="J249" t="n">
+        <v>597</v>
+      </c>
+      <c r="K249" t="s">
+        <v>477</v>
+      </c>
+      <c r="L249" t="s">
+        <v>90</v>
+      </c>
+      <c r="M249" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="553">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1665,6 +1665,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-06 20:26:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07 11:53:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07 13:53:04</t>
   </si>
 </sst>
 </file>
@@ -12202,6 +12208,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>551</v>
+      </c>
+      <c r="B250" t="s">
+        <v>552</v>
+      </c>
+      <c r="C250" t="s">
+        <v>15</v>
+      </c>
+      <c r="D250" t="s">
+        <v>471</v>
+      </c>
+      <c r="E250" t="s">
+        <v>472</v>
+      </c>
+      <c r="F250" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G250" t="s">
+        <v>473</v>
+      </c>
+      <c r="H250" t="n">
+        <v>633</v>
+      </c>
+      <c r="I250" t="s">
+        <v>474</v>
+      </c>
+      <c r="J250" t="n">
+        <v>690</v>
+      </c>
+      <c r="K250" t="s">
+        <v>492</v>
+      </c>
+      <c r="L250" t="s">
+        <v>124</v>
+      </c>
+      <c r="M250" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="555">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1671,6 +1671,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-07 13:53:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07 19:08:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07 21:08:47</t>
   </si>
 </sst>
 </file>
@@ -12249,6 +12255,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>553</v>
+      </c>
+      <c r="B251" t="s">
+        <v>554</v>
+      </c>
+      <c r="C251" t="s">
+        <v>15</v>
+      </c>
+      <c r="D251" t="s">
+        <v>471</v>
+      </c>
+      <c r="E251" t="s">
+        <v>472</v>
+      </c>
+      <c r="F251" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G251" t="s">
+        <v>473</v>
+      </c>
+      <c r="H251" t="n">
+        <v>633</v>
+      </c>
+      <c r="I251" t="s">
+        <v>474</v>
+      </c>
+      <c r="J251" t="n">
+        <v>586</v>
+      </c>
+      <c r="K251" t="s">
+        <v>477</v>
+      </c>
+      <c r="L251" t="s">
+        <v>124</v>
+      </c>
+      <c r="M251" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="557">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1677,6 +1677,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-07 21:08:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08 12:07:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08 14:07:26</t>
   </si>
 </sst>
 </file>
@@ -12296,6 +12302,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>555</v>
+      </c>
+      <c r="B252" t="s">
+        <v>556</v>
+      </c>
+      <c r="C252" t="s">
+        <v>15</v>
+      </c>
+      <c r="D252" t="s">
+        <v>471</v>
+      </c>
+      <c r="E252" t="s">
+        <v>472</v>
+      </c>
+      <c r="F252" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G252" t="s">
+        <v>473</v>
+      </c>
+      <c r="H252" t="n">
+        <v>633</v>
+      </c>
+      <c r="I252" t="s">
+        <v>474</v>
+      </c>
+      <c r="J252" t="n">
+        <v>694</v>
+      </c>
+      <c r="K252" t="s">
+        <v>492</v>
+      </c>
+      <c r="L252" t="s">
+        <v>162</v>
+      </c>
+      <c r="M252" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="559">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1683,6 +1683,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-08 14:07:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08 18:55:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08 20:55:48</t>
   </si>
 </sst>
 </file>
@@ -12343,6 +12349,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>557</v>
+      </c>
+      <c r="B253" t="s">
+        <v>558</v>
+      </c>
+      <c r="C253" t="s">
+        <v>15</v>
+      </c>
+      <c r="D253" t="s">
+        <v>471</v>
+      </c>
+      <c r="E253" t="s">
+        <v>472</v>
+      </c>
+      <c r="F253" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G253" t="s">
+        <v>473</v>
+      </c>
+      <c r="H253" t="n">
+        <v>633</v>
+      </c>
+      <c r="I253" t="s">
+        <v>474</v>
+      </c>
+      <c r="J253" t="n">
+        <v>595</v>
+      </c>
+      <c r="K253" t="s">
+        <v>477</v>
+      </c>
+      <c r="L253" t="s">
+        <v>162</v>
+      </c>
+      <c r="M253" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1689,6 +1689,15 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-08 20:55:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09 11:57:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09 13:57:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3 km</t>
   </si>
 </sst>
 </file>
@@ -12390,6 +12399,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>559</v>
+      </c>
+      <c r="B254" t="s">
+        <v>560</v>
+      </c>
+      <c r="C254" t="s">
+        <v>15</v>
+      </c>
+      <c r="D254" t="s">
+        <v>471</v>
+      </c>
+      <c r="E254" t="s">
+        <v>472</v>
+      </c>
+      <c r="F254" t="n">
+        <v>10313</v>
+      </c>
+      <c r="G254" t="s">
+        <v>561</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I254" t="s">
+        <v>215</v>
+      </c>
+      <c r="J254" t="n">
+        <v>1563</v>
+      </c>
+      <c r="K254" t="s">
+        <v>78</v>
+      </c>
+      <c r="L254" t="s">
+        <v>196</v>
+      </c>
+      <c r="M254" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1698,6 +1698,12 @@
   </si>
   <si>
     <t xml:space="preserve">10.3 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09 18:25:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09 20:25:05</t>
   </si>
 </sst>
 </file>
@@ -12440,6 +12446,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>562</v>
+      </c>
+      <c r="B255" t="s">
+        <v>563</v>
+      </c>
+      <c r="C255" t="s">
+        <v>15</v>
+      </c>
+      <c r="D255" t="s">
+        <v>471</v>
+      </c>
+      <c r="E255" t="s">
+        <v>472</v>
+      </c>
+      <c r="F255" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G255" t="s">
+        <v>473</v>
+      </c>
+      <c r="H255" t="n">
+        <v>633</v>
+      </c>
+      <c r="I255" t="s">
+        <v>474</v>
+      </c>
+      <c r="J255" t="n">
+        <v>598</v>
+      </c>
+      <c r="K255" t="s">
+        <v>477</v>
+      </c>
+      <c r="L255" t="s">
+        <v>196</v>
+      </c>
+      <c r="M255" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="566">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1704,6 +1704,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-09 20:25:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 11:17:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 13:17:26</t>
   </si>
 </sst>
 </file>
@@ -12487,6 +12493,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>564</v>
+      </c>
+      <c r="B256" t="s">
+        <v>565</v>
+      </c>
+      <c r="C256" t="s">
+        <v>15</v>
+      </c>
+      <c r="D256" t="s">
+        <v>471</v>
+      </c>
+      <c r="E256" t="s">
+        <v>472</v>
+      </c>
+      <c r="F256" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G256" t="s">
+        <v>473</v>
+      </c>
+      <c r="H256" t="n">
+        <v>633</v>
+      </c>
+      <c r="I256" t="s">
+        <v>474</v>
+      </c>
+      <c r="J256" t="n">
+        <v>816</v>
+      </c>
+      <c r="K256" t="s">
+        <v>20</v>
+      </c>
+      <c r="L256" t="s">
+        <v>230</v>
+      </c>
+      <c r="M256" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1710,6 +1710,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-10 13:17:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 16:22:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 18:22:16</t>
   </si>
 </sst>
 </file>
@@ -12534,6 +12540,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>566</v>
+      </c>
+      <c r="B257" t="s">
+        <v>567</v>
+      </c>
+      <c r="C257" t="s">
+        <v>15</v>
+      </c>
+      <c r="D257" t="s">
+        <v>471</v>
+      </c>
+      <c r="E257" t="s">
+        <v>472</v>
+      </c>
+      <c r="F257" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G257" t="s">
+        <v>473</v>
+      </c>
+      <c r="H257" t="n">
+        <v>633</v>
+      </c>
+      <c r="I257" t="s">
+        <v>474</v>
+      </c>
+      <c r="J257" t="n">
+        <v>625</v>
+      </c>
+      <c r="K257" t="s">
+        <v>477</v>
+      </c>
+      <c r="L257" t="s">
+        <v>230</v>
+      </c>
+      <c r="M257" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1716,6 +1716,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-10 18:22:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 20:11:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 22:11:45</t>
   </si>
 </sst>
 </file>
@@ -12581,6 +12587,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>568</v>
+      </c>
+      <c r="B258" t="s">
+        <v>569</v>
+      </c>
+      <c r="C258" t="s">
+        <v>15</v>
+      </c>
+      <c r="D258" t="s">
+        <v>471</v>
+      </c>
+      <c r="E258" t="s">
+        <v>472</v>
+      </c>
+      <c r="F258" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G258" t="s">
+        <v>473</v>
+      </c>
+      <c r="H258" t="n">
+        <v>633</v>
+      </c>
+      <c r="I258" t="s">
+        <v>474</v>
+      </c>
+      <c r="J258" t="n">
+        <v>591</v>
+      </c>
+      <c r="K258" t="s">
+        <v>477</v>
+      </c>
+      <c r="L258" t="s">
+        <v>230</v>
+      </c>
+      <c r="M258" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="572">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1722,6 +1722,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-10 22:11:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11 11:29:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11 13:29:11</t>
   </si>
 </sst>
 </file>
@@ -12628,6 +12634,47 @@
         <v>22</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>570</v>
+      </c>
+      <c r="B259" t="s">
+        <v>571</v>
+      </c>
+      <c r="C259" t="s">
+        <v>15</v>
+      </c>
+      <c r="D259" t="s">
+        <v>471</v>
+      </c>
+      <c r="E259" t="s">
+        <v>472</v>
+      </c>
+      <c r="F259" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G259" t="s">
+        <v>473</v>
+      </c>
+      <c r="H259" t="n">
+        <v>633</v>
+      </c>
+      <c r="I259" t="s">
+        <v>474</v>
+      </c>
+      <c r="J259" t="n">
+        <v>580</v>
+      </c>
+      <c r="K259" t="s">
+        <v>477</v>
+      </c>
+      <c r="L259" t="s">
+        <v>21</v>
+      </c>
+      <c r="M259" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1728,6 +1728,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-11 13:29:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11 17:48:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11 19:48:11</t>
   </si>
 </sst>
 </file>
@@ -12675,6 +12681,47 @@
         <v>13</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>572</v>
+      </c>
+      <c r="B260" t="s">
+        <v>573</v>
+      </c>
+      <c r="C260" t="s">
+        <v>15</v>
+      </c>
+      <c r="D260" t="s">
+        <v>471</v>
+      </c>
+      <c r="E260" t="s">
+        <v>472</v>
+      </c>
+      <c r="F260" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G260" t="s">
+        <v>473</v>
+      </c>
+      <c r="H260" t="n">
+        <v>633</v>
+      </c>
+      <c r="I260" t="s">
+        <v>474</v>
+      </c>
+      <c r="J260" t="n">
+        <v>591</v>
+      </c>
+      <c r="K260" t="s">
+        <v>477</v>
+      </c>
+      <c r="L260" t="s">
+        <v>21</v>
+      </c>
+      <c r="M260" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/travel_times.xlsx
+++ b/data/travel_times.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
   <si>
     <t xml:space="preserve">timestamp_utc</t>
   </si>
@@ -1734,6 +1734,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-11 19:48:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12 13:14:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12 15:14:31</t>
   </si>
 </sst>
 </file>
@@ -12722,6 +12728,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>574</v>
+      </c>
+      <c r="B261" t="s">
+        <v>575</v>
+      </c>
+      <c r="C261" t="s">
+        <v>15</v>
+      </c>
+      <c r="D261" t="s">
+        <v>471</v>
+      </c>
+      <c r="E261" t="s">
+        <v>472</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6126</v>
+      </c>
+      <c r="G261" t="s">
+        <v>473</v>
+      </c>
+      <c r="H261" t="n">
+        <v>633</v>
+      </c>
+      <c r="I261" t="s">
+        <v>474</v>
+      </c>
+      <c r="J261" t="n">
+        <v>894</v>
+      </c>
+      <c r="K261" t="s">
+        <v>26</v>
+      </c>
+      <c r="L261" t="s">
+        <v>48</v>
+      </c>
+      <c r="M261" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
